--- a/data/data_xlsx/OPEC消费量预测值.xlsx
+++ b/data/data_xlsx/OPEC消费量预测值.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carl Fu\Desktop\crude-compass-main-main\data\data_xlsx\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FCCF19-50E9-44E9-83C8-DB717D42EBE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9767"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22188" windowHeight="9768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OPEC消费量" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="22">
   <si>
     <t>name</t>
   </si>
@@ -45,9 +38,6 @@
   </si>
   <si>
     <t>消费量</t>
-  </si>
-  <si>
-    <t>百万桶/天</t>
   </si>
   <si>
     <t>经合组织:预期日消费量:战略储备石油</t>
@@ -101,14 +91,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,345 +101,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -463,251 +123,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -722,89 +140,158 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -815,7 +302,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -843,154 +330,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1248,22 +621,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:D250"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:C250"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="54.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,9 +646,8 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1285,13 +657,10 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B3" s="2">
         <v>45016</v>
@@ -1299,11 +668,10 @@
       <c r="C3" s="1">
         <v>27</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
         <v>45107</v>
@@ -1311,11 +679,10 @@
       <c r="C4" s="1">
         <v>26</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>45199</v>
@@ -1323,11 +690,10 @@
       <c r="C5" s="1">
         <v>26</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
         <v>45291</v>
@@ -1335,11 +701,10 @@
       <c r="C6" s="1">
         <v>27</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>45382</v>
@@ -1347,11 +712,10 @@
       <c r="C7" s="1">
         <v>27</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
         <v>45473</v>
@@ -1359,11 +723,10 @@
       <c r="C8" s="1">
         <v>26</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
         <v>45565</v>
@@ -1371,11 +734,10 @@
       <c r="C9" s="1">
         <v>27</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
         <v>45657</v>
@@ -1383,11 +745,10 @@
       <c r="C10" s="1">
         <v>28</v>
       </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>45747</v>
@@ -1395,11 +756,10 @@
       <c r="C11" s="1">
         <v>27</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2">
         <v>45838</v>
@@ -1407,11 +767,10 @@
       <c r="C12" s="1">
         <v>27</v>
       </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2">
         <v>45930</v>
@@ -1419,11 +778,10 @@
       <c r="C13" s="1">
         <v>27</v>
       </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2">
         <v>46022</v>
@@ -1431,11 +789,10 @@
       <c r="C14" s="1">
         <v>28</v>
       </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2">
         <v>45016</v>
@@ -1443,11 +800,10 @@
       <c r="C15" s="1">
         <v>56</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2">
         <v>45107</v>
@@ -1455,11 +811,10 @@
       <c r="C16" s="1">
         <v>55</v>
       </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="2">
         <v>45199</v>
@@ -1467,11 +822,10 @@
       <c r="C17" s="1">
         <v>52</v>
       </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2">
         <v>45291</v>
@@ -1479,11 +833,10 @@
       <c r="C18" s="1">
         <v>51</v>
       </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="2">
         <v>45382</v>
@@ -1491,11 +844,10 @@
       <c r="C19" s="1">
         <v>55</v>
       </c>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2">
         <v>45473</v>
@@ -1503,11 +855,10 @@
       <c r="C20" s="1">
         <v>56</v>
       </c>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2">
         <v>45565</v>
@@ -1515,11 +866,10 @@
       <c r="C21" s="1">
         <v>52</v>
       </c>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2">
         <v>45657</v>
@@ -1527,11 +877,10 @@
       <c r="C22" s="1">
         <v>53</v>
       </c>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:4">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2">
         <v>45747</v>
@@ -1539,11 +888,10 @@
       <c r="C23" s="1">
         <v>57</v>
       </c>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="1:4">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2">
         <v>45838</v>
@@ -1551,11 +899,10 @@
       <c r="C24" s="1">
         <v>55</v>
       </c>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
         <v>45930</v>
@@ -1563,11 +910,10 @@
       <c r="C25" s="1">
         <v>51</v>
       </c>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2">
         <v>46022</v>
@@ -1575,11 +921,10 @@
       <c r="C26" s="1">
         <v>52</v>
       </c>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:4">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" s="2">
         <v>45016</v>
@@ -1587,11 +932,10 @@
       <c r="C27" s="1">
         <v>34</v>
       </c>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="2">
         <v>45107</v>
@@ -1599,11 +943,10 @@
       <c r="C28" s="1">
         <v>34</v>
       </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="2">
         <v>45199</v>
@@ -1611,11 +954,10 @@
       <c r="C29" s="1">
         <v>35</v>
       </c>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:4">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="2">
         <v>45291</v>
@@ -1623,11 +965,10 @@
       <c r="C30" s="1">
         <v>36</v>
       </c>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:4">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" s="2">
         <v>45382</v>
@@ -1635,11 +976,10 @@
       <c r="C31" s="1">
         <v>35</v>
       </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2">
         <v>45473</v>
@@ -1647,11 +987,10 @@
       <c r="C32" s="1">
         <v>33</v>
       </c>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2">
         <v>45565</v>
@@ -1659,11 +998,10 @@
       <c r="C33" s="1">
         <v>35</v>
       </c>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" s="2">
         <v>45657</v>
@@ -1671,11 +1009,10 @@
       <c r="C34" s="1">
         <v>36</v>
       </c>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:4">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35" s="2">
         <v>45747</v>
@@ -1683,11 +1020,10 @@
       <c r="C35" s="1">
         <v>34</v>
       </c>
-      <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="1:4">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2">
         <v>45838</v>
@@ -1695,11 +1031,10 @@
       <c r="C36" s="1">
         <v>33</v>
       </c>
-      <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="1:4">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2">
         <v>45930</v>
@@ -1707,11 +1042,10 @@
       <c r="C37" s="1">
         <v>34</v>
       </c>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38" s="2">
         <v>46022</v>
@@ -1719,11 +1053,10 @@
       <c r="C38" s="1">
         <v>35</v>
       </c>
-      <c r="D38" s="1"/>
-    </row>
-    <row r="39" spans="1:4">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2">
         <v>45016</v>
@@ -1731,11 +1064,10 @@
       <c r="C39" s="1">
         <v>15</v>
       </c>
-      <c r="D39" s="1"/>
-    </row>
-    <row r="40" spans="1:4">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2">
         <v>45107</v>
@@ -1743,11 +1075,10 @@
       <c r="C40" s="1">
         <v>14</v>
       </c>
-      <c r="D40" s="1"/>
-    </row>
-    <row r="41" spans="1:4">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2">
         <v>45199</v>
@@ -1755,11 +1086,10 @@
       <c r="C41" s="1">
         <v>14</v>
       </c>
-      <c r="D41" s="1"/>
-    </row>
-    <row r="42" spans="1:4">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B42" s="2">
         <v>45291</v>
@@ -1767,11 +1097,10 @@
       <c r="C42" s="1">
         <v>14</v>
       </c>
-      <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="1:4">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43" s="2">
         <v>45382</v>
@@ -1779,11 +1108,10 @@
       <c r="C43" s="1">
         <v>14</v>
       </c>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="1:4">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B44" s="2">
         <v>45473</v>
@@ -1791,11 +1119,10 @@
       <c r="C44" s="1">
         <v>15</v>
       </c>
-      <c r="D44" s="1"/>
-    </row>
-    <row r="45" spans="1:4">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2">
         <v>45565</v>
@@ -1803,11 +1130,10 @@
       <c r="C45" s="1">
         <v>15</v>
       </c>
-      <c r="D45" s="1"/>
-    </row>
-    <row r="46" spans="1:4">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B46" s="2">
         <v>45657</v>
@@ -1815,11 +1141,10 @@
       <c r="C46" s="1">
         <v>16</v>
       </c>
-      <c r="D46" s="1"/>
-    </row>
-    <row r="47" spans="1:4">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2">
         <v>45747</v>
@@ -1827,11 +1152,10 @@
       <c r="C47" s="1">
         <v>16</v>
       </c>
-      <c r="D47" s="1"/>
-    </row>
-    <row r="48" spans="1:4">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48" s="2">
         <v>45838</v>
@@ -1839,11 +1163,10 @@
       <c r="C48" s="1">
         <v>16</v>
       </c>
-      <c r="D48" s="1"/>
-    </row>
-    <row r="49" spans="1:4">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49" s="2">
         <v>45930</v>
@@ -1851,11 +1174,10 @@
       <c r="C49" s="1">
         <v>16</v>
       </c>
-      <c r="D49" s="1"/>
-    </row>
-    <row r="50" spans="1:4">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" s="2">
         <v>46022</v>
@@ -1863,11 +1185,10 @@
       <c r="C50" s="1">
         <v>17</v>
       </c>
-      <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="1:4">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" s="2">
         <v>45016</v>
@@ -1875,11 +1196,10 @@
       <c r="C51" s="1">
         <v>61</v>
       </c>
-      <c r="D51" s="1"/>
-    </row>
-    <row r="52" spans="1:4">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" s="2">
         <v>45107</v>
@@ -1887,11 +1207,10 @@
       <c r="C52" s="1">
         <v>61</v>
       </c>
-      <c r="D52" s="1"/>
-    </row>
-    <row r="53" spans="1:4">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" s="2">
         <v>45199</v>
@@ -1899,11 +1218,10 @@
       <c r="C53" s="1">
         <v>61</v>
       </c>
-      <c r="D53" s="1"/>
-    </row>
-    <row r="54" spans="1:4">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="2">
         <v>45291</v>
@@ -1911,11 +1229,10 @@
       <c r="C54" s="1">
         <v>62</v>
       </c>
-      <c r="D54" s="1"/>
-    </row>
-    <row r="55" spans="1:4">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="2">
         <v>45382</v>
@@ -1923,11 +1240,10 @@
       <c r="C55" s="1">
         <v>60</v>
       </c>
-      <c r="D55" s="1"/>
-    </row>
-    <row r="56" spans="1:4">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="2">
         <v>45473</v>
@@ -1935,11 +1251,10 @@
       <c r="C56" s="1">
         <v>61</v>
       </c>
-      <c r="D56" s="1"/>
-    </row>
-    <row r="57" spans="1:4">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" s="2">
         <v>45565</v>
@@ -1947,11 +1262,10 @@
       <c r="C57" s="1">
         <v>61</v>
       </c>
-      <c r="D57" s="1"/>
-    </row>
-    <row r="58" spans="1:4">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="2">
         <v>45657</v>
@@ -1959,11 +1273,10 @@
       <c r="C58" s="1">
         <v>61</v>
       </c>
-      <c r="D58" s="1"/>
-    </row>
-    <row r="59" spans="1:4">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="2">
         <v>45747</v>
@@ -1971,11 +1284,10 @@
       <c r="C59" s="1">
         <v>60</v>
       </c>
-      <c r="D59" s="1"/>
-    </row>
-    <row r="60" spans="1:4">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" s="2">
         <v>45838</v>
@@ -1983,11 +1295,10 @@
       <c r="C60" s="1">
         <v>60</v>
       </c>
-      <c r="D60" s="1"/>
-    </row>
-    <row r="61" spans="1:4">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="2">
         <v>45930</v>
@@ -1995,11 +1306,10 @@
       <c r="C61" s="1">
         <v>62</v>
       </c>
-      <c r="D61" s="1"/>
-    </row>
-    <row r="62" spans="1:4">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="2">
         <v>46022</v>
@@ -2007,11 +1317,10 @@
       <c r="C62" s="1">
         <v>63</v>
       </c>
-      <c r="D62" s="1"/>
-    </row>
-    <row r="63" spans="1:4">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="2">
         <v>45016</v>
@@ -2019,11 +1328,10 @@
       <c r="C63" s="1">
         <v>87</v>
       </c>
-      <c r="D63" s="1"/>
-    </row>
-    <row r="64" spans="1:4">
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="2">
         <v>45107</v>
@@ -2031,11 +1339,10 @@
       <c r="C64" s="1">
         <v>87</v>
       </c>
-      <c r="D64" s="1"/>
-    </row>
-    <row r="65" spans="1:4">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" s="2">
         <v>45199</v>
@@ -2043,11 +1350,10 @@
       <c r="C65" s="1">
         <v>88</v>
       </c>
-      <c r="D65" s="1"/>
-    </row>
-    <row r="66" spans="1:4">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" s="2">
         <v>45291</v>
@@ -2055,11 +1361,10 @@
       <c r="C66" s="1">
         <v>89</v>
       </c>
-      <c r="D66" s="1"/>
-    </row>
-    <row r="67" spans="1:4">
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2">
         <v>45382</v>
@@ -2067,11 +1372,10 @@
       <c r="C67" s="1">
         <v>87</v>
       </c>
-      <c r="D67" s="1"/>
-    </row>
-    <row r="68" spans="1:4">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="2">
         <v>45473</v>
@@ -2079,11 +1383,10 @@
       <c r="C68" s="1">
         <v>88</v>
       </c>
-      <c r="D68" s="1"/>
-    </row>
-    <row r="69" spans="1:4">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2">
         <v>45565</v>
@@ -2091,11 +1394,10 @@
       <c r="C69" s="1">
         <v>87</v>
       </c>
-      <c r="D69" s="1"/>
-    </row>
-    <row r="70" spans="1:4">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2">
         <v>45657</v>
@@ -2103,11 +1405,10 @@
       <c r="C70" s="1">
         <v>88</v>
       </c>
-      <c r="D70" s="1"/>
-    </row>
-    <row r="71" spans="1:4">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" s="2">
         <v>45747</v>
@@ -2115,11 +1416,10 @@
       <c r="C71" s="1">
         <v>87</v>
       </c>
-      <c r="D71" s="1"/>
-    </row>
-    <row r="72" spans="1:4">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" s="2">
         <v>45838</v>
@@ -2127,11 +1427,10 @@
       <c r="C72" s="1">
         <v>87</v>
       </c>
-      <c r="D72" s="1"/>
-    </row>
-    <row r="73" spans="1:4">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" s="2">
         <v>45930</v>
@@ -2139,11 +1438,10 @@
       <c r="C73" s="1">
         <v>89</v>
       </c>
-      <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="1:4">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2">
         <v>46022</v>
@@ -2151,11 +1449,10 @@
       <c r="C74" s="1">
         <v>90</v>
       </c>
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="1:4">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="2">
         <v>45016</v>
@@ -2163,11 +1460,10 @@
       <c r="C75" s="1">
         <v>51</v>
       </c>
-      <c r="D75" s="1"/>
-    </row>
-    <row r="76" spans="1:4">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" s="2">
         <v>45107</v>
@@ -2175,11 +1471,10 @@
       <c r="C76" s="1">
         <v>51</v>
       </c>
-      <c r="D76" s="1"/>
-    </row>
-    <row r="77" spans="1:4">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" s="2">
         <v>45199</v>
@@ -2187,11 +1482,10 @@
       <c r="C77" s="1">
         <v>49</v>
       </c>
-      <c r="D77" s="1"/>
-    </row>
-    <row r="78" spans="1:4">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B78" s="2">
         <v>45291</v>
@@ -2199,11 +1493,10 @@
       <c r="C78" s="1">
         <v>47</v>
       </c>
-      <c r="D78" s="1"/>
-    </row>
-    <row r="79" spans="1:4">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B79" s="2">
         <v>45382</v>
@@ -2211,11 +1504,10 @@
       <c r="C79" s="1">
         <v>48</v>
       </c>
-      <c r="D79" s="1"/>
-    </row>
-    <row r="80" spans="1:4">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B80" s="2">
         <v>45473</v>
@@ -2223,11 +1515,10 @@
       <c r="C80" s="1">
         <v>50</v>
       </c>
-      <c r="D80" s="1"/>
-    </row>
-    <row r="81" spans="1:4">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B81" s="2">
         <v>45565</v>
@@ -2235,11 +1526,10 @@
       <c r="C81" s="1">
         <v>48</v>
       </c>
-      <c r="D81" s="1"/>
-    </row>
-    <row r="82" spans="1:4">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" s="2">
         <v>45657</v>
@@ -2247,11 +1537,10 @@
       <c r="C82" s="1">
         <v>46</v>
       </c>
-      <c r="D82" s="1"/>
-    </row>
-    <row r="83" spans="1:4">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B83" s="2">
         <v>45747</v>
@@ -2259,11 +1548,10 @@
       <c r="C83" s="1">
         <v>51</v>
       </c>
-      <c r="D83" s="1"/>
-    </row>
-    <row r="84" spans="1:4">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B84" s="2">
         <v>45838</v>
@@ -2271,11 +1559,10 @@
       <c r="C84" s="1">
         <v>53</v>
       </c>
-      <c r="D84" s="1"/>
-    </row>
-    <row r="85" spans="1:4">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" s="2">
         <v>45930</v>
@@ -2283,11 +1570,10 @@
       <c r="C85" s="1">
         <v>48</v>
       </c>
-      <c r="D85" s="1"/>
-    </row>
-    <row r="86" spans="1:4">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B86" s="2">
         <v>46022</v>
@@ -2295,11 +1581,10 @@
       <c r="C86" s="1">
         <v>49</v>
       </c>
-      <c r="D86" s="1"/>
-    </row>
-    <row r="87" spans="1:4">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B87" s="2">
         <v>45016</v>
@@ -2307,11 +1592,10 @@
       <c r="C87" s="1">
         <v>68</v>
       </c>
-      <c r="D87" s="1"/>
-    </row>
-    <row r="88" spans="1:4">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B88" s="2">
         <v>45107</v>
@@ -2319,11 +1603,10 @@
       <c r="C88" s="1">
         <v>67</v>
       </c>
-      <c r="D88" s="1"/>
-    </row>
-    <row r="89" spans="1:4">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B89" s="2">
         <v>45199</v>
@@ -2331,11 +1614,10 @@
       <c r="C89" s="1">
         <v>69</v>
       </c>
-      <c r="D89" s="1"/>
-    </row>
-    <row r="90" spans="1:4">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B90" s="2">
         <v>45291</v>
@@ -2343,11 +1625,10 @@
       <c r="C90" s="1">
         <v>71</v>
       </c>
-      <c r="D90" s="1"/>
-    </row>
-    <row r="91" spans="1:4">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B91" s="2">
         <v>45382</v>
@@ -2355,11 +1636,10 @@
       <c r="C91" s="1">
         <v>69</v>
       </c>
-      <c r="D91" s="1"/>
-    </row>
-    <row r="92" spans="1:4">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92" s="2">
         <v>45473</v>
@@ -2367,11 +1647,10 @@
       <c r="C92" s="1">
         <v>68</v>
       </c>
-      <c r="D92" s="1"/>
-    </row>
-    <row r="93" spans="1:4">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93" s="2">
         <v>45565</v>
@@ -2379,11 +1658,10 @@
       <c r="C93" s="1">
         <v>68</v>
       </c>
-      <c r="D93" s="1"/>
-    </row>
-    <row r="94" spans="1:4">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B94" s="2">
         <v>45657</v>
@@ -2391,11 +1669,10 @@
       <c r="C94" s="1">
         <v>72</v>
       </c>
-      <c r="D94" s="1"/>
-    </row>
-    <row r="95" spans="1:4">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B95" s="2">
         <v>45747</v>
@@ -2403,11 +1680,10 @@
       <c r="C95" s="1">
         <v>69</v>
       </c>
-      <c r="D95" s="1"/>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96" s="2">
         <v>45838</v>
@@ -2415,11 +1691,10 @@
       <c r="C96" s="1">
         <v>67</v>
       </c>
-      <c r="D96" s="1"/>
-    </row>
-    <row r="97" spans="1:4">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B97" s="2">
         <v>45930</v>
@@ -2427,11 +1702,10 @@
       <c r="C97" s="1">
         <v>71</v>
       </c>
-      <c r="D97" s="1"/>
-    </row>
-    <row r="98" spans="1:4">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B98" s="2">
         <v>46022</v>
@@ -2439,11 +1713,10 @@
       <c r="C98" s="1">
         <v>71</v>
       </c>
-      <c r="D98" s="1"/>
-    </row>
-    <row r="99" spans="1:4">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B99" s="2">
         <v>45016</v>
@@ -2451,11 +1724,10 @@
       <c r="C99" s="1">
         <v>59</v>
       </c>
-      <c r="D99" s="1"/>
-    </row>
-    <row r="100" spans="1:4">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B100" s="2">
         <v>45107</v>
@@ -2463,11 +1735,10 @@
       <c r="C100" s="1">
         <v>60</v>
       </c>
-      <c r="D100" s="1"/>
-    </row>
-    <row r="101" spans="1:4">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B101" s="2">
         <v>45199</v>
@@ -2475,11 +1746,10 @@
       <c r="C101" s="1">
         <v>61</v>
       </c>
-      <c r="D101" s="1"/>
-    </row>
-    <row r="102" spans="1:4">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B102" s="2">
         <v>45291</v>
@@ -2487,11 +1757,10 @@
       <c r="C102" s="1">
         <v>62</v>
       </c>
-      <c r="D102" s="1"/>
-    </row>
-    <row r="103" spans="1:4">
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B103" s="2">
         <v>45382</v>
@@ -2499,11 +1768,10 @@
       <c r="C103" s="1">
         <v>59</v>
       </c>
-      <c r="D103" s="1"/>
-    </row>
-    <row r="104" spans="1:4">
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B104" s="2">
         <v>45473</v>
@@ -2511,11 +1779,10 @@
       <c r="C104" s="1">
         <v>61</v>
       </c>
-      <c r="D104" s="1"/>
-    </row>
-    <row r="105" spans="1:4">
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B105" s="2">
         <v>45565</v>
@@ -2523,11 +1790,10 @@
       <c r="C105" s="1">
         <v>60</v>
       </c>
-      <c r="D105" s="1"/>
-    </row>
-    <row r="106" spans="1:4">
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B106" s="2">
         <v>45657</v>
@@ -2535,11 +1801,10 @@
       <c r="C106" s="1">
         <v>60</v>
       </c>
-      <c r="D106" s="1"/>
-    </row>
-    <row r="107" spans="1:4">
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B107" s="2">
         <v>45747</v>
@@ -2547,11 +1812,10 @@
       <c r="C107" s="1">
         <v>58</v>
       </c>
-      <c r="D107" s="1"/>
-    </row>
-    <row r="108" spans="1:4">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B108" s="2">
         <v>45838</v>
@@ -2559,11 +1823,10 @@
       <c r="C108" s="1">
         <v>58</v>
       </c>
-      <c r="D108" s="1"/>
-    </row>
-    <row r="109" spans="1:4">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B109" s="2">
         <v>45930</v>
@@ -2571,11 +1834,10 @@
       <c r="C109" s="1">
         <v>61</v>
       </c>
-      <c r="D109" s="1"/>
-    </row>
-    <row r="110" spans="1:4">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B110" s="2">
         <v>46022</v>
@@ -2583,11 +1845,10 @@
       <c r="C110" s="1">
         <v>63</v>
       </c>
-      <c r="D110" s="1"/>
-    </row>
-    <row r="111" spans="1:4">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B111" s="2">
         <v>45016</v>
@@ -2595,11 +1856,10 @@
       <c r="C111" s="1">
         <v>101.57</v>
       </c>
-      <c r="D111" s="1"/>
-    </row>
-    <row r="112" spans="1:4">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B112" s="2">
         <v>45107</v>
@@ -2607,11 +1867,10 @@
       <c r="C112" s="1">
         <v>101.47</v>
       </c>
-      <c r="D112" s="1"/>
-    </row>
-    <row r="113" spans="1:4">
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B113" s="2">
         <v>45199</v>
@@ -2619,11 +1878,10 @@
       <c r="C113" s="1">
         <v>102.12</v>
       </c>
-      <c r="D113" s="1"/>
-    </row>
-    <row r="114" spans="1:4">
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B114" s="2">
         <v>45291</v>
@@ -2631,11 +1889,10 @@
       <c r="C114" s="1">
         <v>103.28</v>
       </c>
-      <c r="D114" s="1"/>
-    </row>
-    <row r="115" spans="1:4">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B115" s="2">
         <v>45382</v>
@@ -2643,11 +1900,10 @@
       <c r="C115" s="1">
         <v>102.8</v>
       </c>
-      <c r="D115" s="1"/>
-    </row>
-    <row r="116" spans="1:4">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B116" s="2">
         <v>45473</v>
@@ -2655,11 +1911,10 @@
       <c r="C116" s="1">
         <v>103</v>
       </c>
-      <c r="D116" s="1"/>
-    </row>
-    <row r="117" spans="1:4">
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B117" s="2">
         <v>45565</v>
@@ -2667,11 +1922,10 @@
       <c r="C117" s="1">
         <v>104</v>
       </c>
-      <c r="D117" s="1"/>
-    </row>
-    <row r="118" spans="1:4">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B118" s="2">
         <v>45657</v>
@@ -2679,11 +1933,10 @@
       <c r="C118" s="1">
         <v>105.5</v>
       </c>
-      <c r="D118" s="1"/>
-    </row>
-    <row r="119" spans="1:4">
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B119" s="2">
         <v>45747</v>
@@ -2691,11 +1944,10 @@
       <c r="C119" s="1">
         <v>104.3</v>
       </c>
-      <c r="D119" s="1"/>
-    </row>
-    <row r="120" spans="1:4">
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B120" s="2">
         <v>45838</v>
@@ -2703,11 +1955,10 @@
       <c r="C120" s="1">
         <v>104.2</v>
       </c>
-      <c r="D120" s="1"/>
-    </row>
-    <row r="121" spans="1:4">
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B121" s="2">
         <v>45930</v>
@@ -2715,11 +1966,10 @@
       <c r="C121" s="1">
         <v>105.5</v>
       </c>
-      <c r="D121" s="1"/>
-    </row>
-    <row r="122" spans="1:4">
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B122" s="2">
         <v>46022</v>
@@ -2727,11 +1977,10 @@
       <c r="C122" s="1">
         <v>106.6</v>
       </c>
-      <c r="D122" s="1"/>
-    </row>
-    <row r="123" spans="1:4">
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B123" s="2">
         <v>46112</v>
@@ -2739,11 +1988,10 @@
       <c r="C123" s="1">
         <v>105.6</v>
       </c>
-      <c r="D123" s="1"/>
-    </row>
-    <row r="124" spans="1:4">
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B124" s="2">
         <v>46203</v>
@@ -2751,11 +1999,10 @@
       <c r="C124" s="1">
         <v>105.6</v>
       </c>
-      <c r="D124" s="1"/>
-    </row>
-    <row r="125" spans="1:4">
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B125" s="2">
         <v>46295</v>
@@ -2763,11 +2010,10 @@
       <c r="C125" s="1">
         <v>107</v>
       </c>
-      <c r="D125" s="1"/>
-    </row>
-    <row r="126" spans="1:4">
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B126" s="2">
         <v>46387</v>
@@ -2775,11 +2021,10 @@
       <c r="C126" s="1">
         <v>107.9</v>
       </c>
-      <c r="D126" s="1"/>
-    </row>
-    <row r="127" spans="1:4">
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B127" s="2">
         <v>46477</v>
@@ -2787,11 +2032,10 @@
       <c r="C127" s="1">
         <v>106.9</v>
       </c>
-      <c r="D127" s="1"/>
-    </row>
-    <row r="128" spans="1:4">
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B128" s="2">
         <v>46568</v>
@@ -2799,11 +2043,10 @@
       <c r="C128" s="1">
         <v>106.8</v>
       </c>
-      <c r="D128" s="1"/>
-    </row>
-    <row r="129" spans="1:4">
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B129" s="2">
         <v>46660</v>
@@ -2811,11 +2054,10 @@
       <c r="C129" s="1">
         <v>108.5</v>
       </c>
-      <c r="D129" s="1"/>
-    </row>
-    <row r="130" spans="1:4">
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B130" s="2">
         <v>46752</v>
@@ -2823,11 +2065,10 @@
       <c r="C130" s="1">
         <v>109.3</v>
       </c>
-      <c r="D130" s="1"/>
-    </row>
-    <row r="131" spans="1:4">
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B131" s="2">
         <v>45016</v>
@@ -2835,11 +2076,10 @@
       <c r="C131" s="1">
         <v>45.43</v>
       </c>
-      <c r="D131" s="1"/>
-    </row>
-    <row r="132" spans="1:4">
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B132" s="2">
         <v>45107</v>
@@ -2847,11 +2087,10 @@
       <c r="C132" s="1">
         <v>45.71</v>
       </c>
-      <c r="D132" s="1"/>
-    </row>
-    <row r="133" spans="1:4">
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B133" s="2">
         <v>45199</v>
@@ -2859,11 +2098,10 @@
       <c r="C133" s="1">
         <v>46.2</v>
       </c>
-      <c r="D133" s="1"/>
-    </row>
-    <row r="134" spans="1:4">
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B134" s="2">
         <v>45291</v>
@@ -2871,11 +2109,10 @@
       <c r="C134" s="1">
         <v>45.93</v>
       </c>
-      <c r="D134" s="1"/>
-    </row>
-    <row r="135" spans="1:4">
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B135" s="2">
         <v>45382</v>
@@ -2883,11 +2120,10 @@
       <c r="C135" s="1">
         <v>44.8</v>
       </c>
-      <c r="D135" s="1"/>
-    </row>
-    <row r="136" spans="1:4">
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B136" s="2">
         <v>45473</v>
@@ -2895,11 +2131,10 @@
       <c r="C136" s="1">
         <v>45.6</v>
       </c>
-      <c r="D136" s="1"/>
-    </row>
-    <row r="137" spans="1:4">
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B137" s="2">
         <v>45565</v>
@@ -2907,11 +2142,10 @@
       <c r="C137" s="1">
         <v>46.4</v>
       </c>
-      <c r="D137" s="1"/>
-    </row>
-    <row r="138" spans="1:4">
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B138" s="2">
         <v>45657</v>
@@ -2919,11 +2153,10 @@
       <c r="C138" s="1">
         <v>46.3</v>
       </c>
-      <c r="D138" s="1"/>
-    </row>
-    <row r="139" spans="1:4">
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B139" s="2">
         <v>45747</v>
@@ -2931,11 +2164,10 @@
       <c r="C139" s="1">
         <v>45.2</v>
       </c>
-      <c r="D139" s="1"/>
-    </row>
-    <row r="140" spans="1:4">
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B140" s="2">
         <v>45838</v>
@@ -2943,11 +2175,10 @@
       <c r="C140" s="1">
         <v>45.6</v>
       </c>
-      <c r="D140" s="1"/>
-    </row>
-    <row r="141" spans="1:4">
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B141" s="2">
         <v>45930</v>
@@ -2955,11 +2186,10 @@
       <c r="C141" s="1">
         <v>46.5</v>
       </c>
-      <c r="D141" s="1"/>
-    </row>
-    <row r="142" spans="1:4">
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B142" s="2">
         <v>46022</v>
@@ -2967,11 +2197,10 @@
       <c r="C142" s="1">
         <v>46.5</v>
       </c>
-      <c r="D142" s="1"/>
-    </row>
-    <row r="143" spans="1:4">
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B143" s="2">
         <v>46112</v>
@@ -2979,11 +2208,10 @@
       <c r="C143" s="1">
         <v>45.3</v>
       </c>
-      <c r="D143" s="1"/>
-    </row>
-    <row r="144" spans="1:4">
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B144" s="2">
         <v>46203</v>
@@ -2991,11 +2219,10 @@
       <c r="C144" s="1">
         <v>45.8</v>
       </c>
-      <c r="D144" s="1"/>
-    </row>
-    <row r="145" spans="1:4">
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B145" s="2">
         <v>46295</v>
@@ -3003,11 +2230,10 @@
       <c r="C145" s="1">
         <v>46.7</v>
       </c>
-      <c r="D145" s="1"/>
-    </row>
-    <row r="146" spans="1:4">
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B146" s="2">
         <v>46387</v>
@@ -3015,11 +2241,10 @@
       <c r="C146" s="1">
         <v>46.5</v>
       </c>
-      <c r="D146" s="1"/>
-    </row>
-    <row r="147" spans="1:4">
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B147" s="2">
         <v>46477</v>
@@ -3027,11 +2252,10 @@
       <c r="C147" s="1">
         <v>45.4</v>
       </c>
-      <c r="D147" s="1"/>
-    </row>
-    <row r="148" spans="1:4">
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B148" s="2">
         <v>46568</v>
@@ -3039,11 +2263,10 @@
       <c r="C148" s="1">
         <v>45.9</v>
       </c>
-      <c r="D148" s="1"/>
-    </row>
-    <row r="149" spans="1:4">
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B149" s="2">
         <v>46660</v>
@@ -3051,11 +2274,10 @@
       <c r="C149" s="1">
         <v>46.8</v>
       </c>
-      <c r="D149" s="1"/>
-    </row>
-    <row r="150" spans="1:4">
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B150" s="2">
         <v>46752</v>
@@ -3063,11 +2285,10 @@
       <c r="C150" s="1">
         <v>46.6</v>
       </c>
-      <c r="D150" s="1"/>
-    </row>
-    <row r="151" spans="1:4">
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B151" s="2">
         <v>45016</v>
@@ -3075,11 +2296,10 @@
       <c r="C151" s="1">
         <v>24.52</v>
       </c>
-      <c r="D151" s="1"/>
-    </row>
-    <row r="152" spans="1:4">
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B152" s="2">
         <v>45107</v>
@@ -3087,11 +2307,10 @@
       <c r="C152" s="1">
         <v>25.21</v>
       </c>
-      <c r="D152" s="1"/>
-    </row>
-    <row r="153" spans="1:4">
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B153" s="2">
         <v>45199</v>
@@ -3099,11 +2318,10 @@
       <c r="C153" s="1">
         <v>25.47</v>
       </c>
-      <c r="D153" s="1"/>
-    </row>
-    <row r="154" spans="1:4">
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B154" s="2">
         <v>45291</v>
@@ -3111,11 +2329,10 @@
       <c r="C154" s="1">
         <v>24.94</v>
       </c>
-      <c r="D154" s="1"/>
-    </row>
-    <row r="155" spans="1:4">
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B155" s="2">
         <v>45382</v>
@@ -3123,11 +2340,10 @@
       <c r="C155" s="1">
         <v>24.4</v>
       </c>
-      <c r="D155" s="1"/>
-    </row>
-    <row r="156" spans="1:4">
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B156" s="2">
         <v>45473</v>
@@ -3135,11 +2351,10 @@
       <c r="C156" s="1">
         <v>25</v>
       </c>
-      <c r="D156" s="1"/>
-    </row>
-    <row r="157" spans="1:4">
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B157" s="2">
         <v>45565</v>
@@ -3147,11 +2362,10 @@
       <c r="C157" s="1">
         <v>25.3</v>
       </c>
-      <c r="D157" s="1"/>
-    </row>
-    <row r="158" spans="1:4">
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B158" s="2">
         <v>45657</v>
@@ -3159,11 +2373,10 @@
       <c r="C158" s="1">
         <v>25.4</v>
       </c>
-      <c r="D158" s="1"/>
-    </row>
-    <row r="159" spans="1:4">
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B159" s="2">
         <v>45747</v>
@@ -3171,11 +2384,10 @@
       <c r="C159" s="1">
         <v>25</v>
       </c>
-      <c r="D159" s="1"/>
-    </row>
-    <row r="160" spans="1:4">
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B160" s="2">
         <v>45838</v>
@@ -3183,11 +2395,10 @@
       <c r="C160" s="1">
         <v>25.2</v>
       </c>
-      <c r="D160" s="1"/>
-    </row>
-    <row r="161" spans="1:4">
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B161" s="2">
         <v>45930</v>
@@ -3195,11 +2406,10 @@
       <c r="C161" s="1">
         <v>25.8</v>
       </c>
-      <c r="D161" s="1"/>
-    </row>
-    <row r="162" spans="1:4">
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B162" s="2">
         <v>46022</v>
@@ -3207,11 +2417,10 @@
       <c r="C162" s="1">
         <v>25.6</v>
       </c>
-      <c r="D162" s="1"/>
-    </row>
-    <row r="163" spans="1:4">
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B163" s="2">
         <v>46112</v>
@@ -3219,11 +2428,10 @@
       <c r="C163" s="1">
         <v>25.1</v>
       </c>
-      <c r="D163" s="1"/>
-    </row>
-    <row r="164" spans="1:4">
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B164" s="2">
         <v>46203</v>
@@ -3231,11 +2439,10 @@
       <c r="C164" s="1">
         <v>25.3</v>
       </c>
-      <c r="D164" s="1"/>
-    </row>
-    <row r="165" spans="1:4">
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B165" s="2">
         <v>46295</v>
@@ -3243,11 +2450,10 @@
       <c r="C165" s="1">
         <v>26.1</v>
       </c>
-      <c r="D165" s="1"/>
-    </row>
-    <row r="166" spans="1:4">
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B166" s="2">
         <v>46387</v>
@@ -3255,11 +2461,10 @@
       <c r="C166" s="1">
         <v>25.7</v>
       </c>
-      <c r="D166" s="1"/>
-    </row>
-    <row r="167" spans="1:4">
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B167" s="2">
         <v>46477</v>
@@ -3267,11 +2472,10 @@
       <c r="C167" s="1">
         <v>25.1</v>
       </c>
-      <c r="D167" s="1"/>
-    </row>
-    <row r="168" spans="1:4">
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B168" s="2">
         <v>46568</v>
@@ -3279,11 +2483,10 @@
       <c r="C168" s="1">
         <v>25.4</v>
       </c>
-      <c r="D168" s="1"/>
-    </row>
-    <row r="169" spans="1:4">
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B169" s="2">
         <v>46660</v>
@@ -3291,11 +2494,10 @@
       <c r="C169" s="1">
         <v>26.2</v>
       </c>
-      <c r="D169" s="1"/>
-    </row>
-    <row r="170" spans="1:4">
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B170" s="2">
         <v>46752</v>
@@ -3303,11 +2505,10 @@
       <c r="C170" s="1">
         <v>25.8</v>
       </c>
-      <c r="D170" s="1"/>
-    </row>
-    <row r="171" spans="1:4">
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B171" s="2">
         <v>45016</v>
@@ -3315,11 +2516,10 @@
       <c r="C171" s="1">
         <v>13.1</v>
       </c>
-      <c r="D171" s="1"/>
-    </row>
-    <row r="172" spans="1:4">
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B172" s="2">
         <v>45107</v>
@@ -3327,11 +2527,10 @@
       <c r="C172" s="1">
         <v>13.54</v>
       </c>
-      <c r="D172" s="1"/>
-    </row>
-    <row r="173" spans="1:4">
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B173" s="2">
         <v>45199</v>
@@ -3339,11 +2538,10 @@
       <c r="C173" s="1">
         <v>13.67</v>
       </c>
-      <c r="D173" s="1"/>
-    </row>
-    <row r="174" spans="1:4">
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B174" s="2">
         <v>45291</v>
@@ -3351,11 +2549,10 @@
       <c r="C174" s="1">
         <v>13.34</v>
       </c>
-      <c r="D174" s="1"/>
-    </row>
-    <row r="175" spans="1:4">
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B175" s="2">
         <v>45382</v>
@@ -3363,11 +2560,10 @@
       <c r="C175" s="1">
         <v>12.9</v>
       </c>
-      <c r="D175" s="1"/>
-    </row>
-    <row r="176" spans="1:4">
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B176" s="2">
         <v>45473</v>
@@ -3375,11 +2571,10 @@
       <c r="C176" s="1">
         <v>13.6</v>
       </c>
-      <c r="D176" s="1"/>
-    </row>
-    <row r="177" spans="1:4">
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B177" s="2">
         <v>45565</v>
@@ -3387,11 +2582,10 @@
       <c r="C177" s="1">
         <v>14.2</v>
       </c>
-      <c r="D177" s="1"/>
-    </row>
-    <row r="178" spans="1:4">
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B178" s="2">
         <v>45657</v>
@@ -3399,11 +2593,10 @@
       <c r="C178" s="1">
         <v>13.4</v>
       </c>
-      <c r="D178" s="1"/>
-    </row>
-    <row r="179" spans="1:4">
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B179" s="2">
         <v>45747</v>
@@ -3411,11 +2604,10 @@
       <c r="C179" s="1">
         <v>12.9</v>
       </c>
-      <c r="D179" s="1"/>
-    </row>
-    <row r="180" spans="1:4">
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B180" s="2">
         <v>45838</v>
@@ -3423,11 +2615,10 @@
       <c r="C180" s="1">
         <v>13.6</v>
       </c>
-      <c r="D180" s="1"/>
-    </row>
-    <row r="181" spans="1:4">
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B181" s="2">
         <v>45930</v>
@@ -3435,11 +2626,10 @@
       <c r="C181" s="1">
         <v>13.8</v>
       </c>
-      <c r="D181" s="1"/>
-    </row>
-    <row r="182" spans="1:4">
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B182" s="2">
         <v>46022</v>
@@ -3447,11 +2637,10 @@
       <c r="C182" s="1">
         <v>13.5</v>
       </c>
-      <c r="D182" s="1"/>
-    </row>
-    <row r="183" spans="1:4">
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B183" s="2">
         <v>46112</v>
@@ -3459,11 +2648,10 @@
       <c r="C183" s="1">
         <v>12.9</v>
       </c>
-      <c r="D183" s="1"/>
-    </row>
-    <row r="184" spans="1:4">
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B184" s="2">
         <v>46203</v>
@@ -3471,11 +2659,10 @@
       <c r="C184" s="1">
         <v>13.7</v>
       </c>
-      <c r="D184" s="1"/>
-    </row>
-    <row r="185" spans="1:4">
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B185" s="2">
         <v>46295</v>
@@ -3483,11 +2670,10 @@
       <c r="C185" s="1">
         <v>13.8</v>
       </c>
-      <c r="D185" s="1"/>
-    </row>
-    <row r="186" spans="1:4">
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B186" s="2">
         <v>46387</v>
@@ -3495,11 +2681,10 @@
       <c r="C186" s="1">
         <v>13.5</v>
       </c>
-      <c r="D186" s="1"/>
-    </row>
-    <row r="187" spans="1:4">
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B187" s="2">
         <v>46477</v>
@@ -3507,11 +2692,10 @@
       <c r="C187" s="1">
         <v>13</v>
       </c>
-      <c r="D187" s="1"/>
-    </row>
-    <row r="188" spans="1:4">
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B188" s="2">
         <v>46568</v>
@@ -3519,11 +2703,10 @@
       <c r="C188" s="1">
         <v>13.7</v>
       </c>
-      <c r="D188" s="1"/>
-    </row>
-    <row r="189" spans="1:4">
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B189" s="2">
         <v>46660</v>
@@ -3531,11 +2714,10 @@
       <c r="C189" s="1">
         <v>13.8</v>
       </c>
-      <c r="D189" s="1"/>
-    </row>
-    <row r="190" spans="1:4">
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B190" s="2">
         <v>46752</v>
@@ -3543,11 +2725,10 @@
       <c r="C190" s="1">
         <v>13.5</v>
       </c>
-      <c r="D190" s="1"/>
-    </row>
-    <row r="191" spans="1:4">
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B191" s="2">
         <v>45016</v>
@@ -3555,11 +2736,10 @@
       <c r="C191" s="1">
         <v>7.81</v>
       </c>
-      <c r="D191" s="1"/>
-    </row>
-    <row r="192" spans="1:4">
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B192" s="2">
         <v>45107</v>
@@ -3567,11 +2747,10 @@
       <c r="C192" s="1">
         <v>6.96</v>
       </c>
-      <c r="D192" s="1"/>
-    </row>
-    <row r="193" spans="1:4">
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B193" s="2">
         <v>45199</v>
@@ -3579,11 +2758,10 @@
       <c r="C193" s="1">
         <v>7.07</v>
       </c>
-      <c r="D193" s="1"/>
-    </row>
-    <row r="194" spans="1:4">
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B194" s="2">
         <v>45291</v>
@@ -3591,11 +2769,10 @@
       <c r="C194" s="1">
         <v>7.65</v>
       </c>
-      <c r="D194" s="1"/>
-    </row>
-    <row r="195" spans="1:4">
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B195" s="2">
         <v>45382</v>
@@ -3603,11 +2780,10 @@
       <c r="C195" s="1">
         <v>7.5</v>
       </c>
-      <c r="D195" s="1"/>
-    </row>
-    <row r="196" spans="1:4">
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B196" s="2">
         <v>45473</v>
@@ -3615,11 +2791,10 @@
       <c r="C196" s="1">
         <v>7</v>
       </c>
-      <c r="D196" s="1"/>
-    </row>
-    <row r="197" spans="1:4">
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B197" s="2">
         <v>45565</v>
@@ -3627,11 +2802,10 @@
       <c r="C197" s="1">
         <v>6.9</v>
       </c>
-      <c r="D197" s="1"/>
-    </row>
-    <row r="198" spans="1:4">
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B198" s="2">
         <v>45657</v>
@@ -3639,11 +2813,10 @@
       <c r="C198" s="1">
         <v>7.4</v>
       </c>
-      <c r="D198" s="1"/>
-    </row>
-    <row r="199" spans="1:4">
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B199" s="2">
         <v>45747</v>
@@ -3651,11 +2824,10 @@
       <c r="C199" s="1">
         <v>7.3</v>
       </c>
-      <c r="D199" s="1"/>
-    </row>
-    <row r="200" spans="1:4">
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B200" s="2">
         <v>45838</v>
@@ -3663,11 +2835,10 @@
       <c r="C200" s="1">
         <v>6.8</v>
       </c>
-      <c r="D200" s="1"/>
-    </row>
-    <row r="201" spans="1:4">
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B201" s="2">
         <v>45930</v>
@@ -3675,11 +2846,10 @@
       <c r="C201" s="1">
         <v>6.9</v>
       </c>
-      <c r="D201" s="1"/>
-    </row>
-    <row r="202" spans="1:4">
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B202" s="2">
         <v>46022</v>
@@ -3687,11 +2857,10 @@
       <c r="C202" s="1">
         <v>7.4</v>
       </c>
-      <c r="D202" s="1"/>
-    </row>
-    <row r="203" spans="1:4">
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B203" s="2">
         <v>46112</v>
@@ -3699,11 +2868,10 @@
       <c r="C203" s="1">
         <v>7.3</v>
       </c>
-      <c r="D203" s="1"/>
-    </row>
-    <row r="204" spans="1:4">
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B204" s="2">
         <v>46203</v>
@@ -3711,11 +2879,10 @@
       <c r="C204" s="1">
         <v>6.8</v>
       </c>
-      <c r="D204" s="1"/>
-    </row>
-    <row r="205" spans="1:4">
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B205" s="2">
         <v>46295</v>
@@ -3723,11 +2890,10 @@
       <c r="C205" s="1">
         <v>6.9</v>
       </c>
-      <c r="D205" s="1"/>
-    </row>
-    <row r="206" spans="1:4">
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B206" s="2">
         <v>46387</v>
@@ -3735,11 +2901,10 @@
       <c r="C206" s="1">
         <v>7.4</v>
       </c>
-      <c r="D206" s="1"/>
-    </row>
-    <row r="207" spans="1:4">
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B207" s="2">
         <v>46477</v>
@@ -3747,11 +2912,10 @@
       <c r="C207" s="1">
         <v>7.3</v>
       </c>
-      <c r="D207" s="1"/>
-    </row>
-    <row r="208" spans="1:4">
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B208" s="2">
         <v>46568</v>
@@ -3759,11 +2923,10 @@
       <c r="C208" s="1">
         <v>6.8</v>
       </c>
-      <c r="D208" s="1"/>
-    </row>
-    <row r="209" spans="1:4">
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B209" s="2">
         <v>46660</v>
@@ -3771,11 +2934,10 @@
       <c r="C209" s="1">
         <v>6.9</v>
       </c>
-      <c r="D209" s="1"/>
-    </row>
-    <row r="210" spans="1:4">
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B210" s="2">
         <v>46752</v>
@@ -3783,11 +2945,10 @@
       <c r="C210" s="1">
         <v>7.4</v>
       </c>
-      <c r="D210" s="1"/>
-    </row>
-    <row r="211" spans="1:4">
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B211" s="2">
         <v>45016</v>
@@ -3795,11 +2956,10 @@
       <c r="C211" s="1">
         <v>0.79</v>
       </c>
-      <c r="D211" s="1"/>
-    </row>
-    <row r="212" spans="1:4">
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B212" s="2">
         <v>45107</v>
@@ -3807,11 +2967,10 @@
       <c r="C212" s="1">
         <v>0.77</v>
       </c>
-      <c r="D212" s="1"/>
-    </row>
-    <row r="213" spans="1:4">
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B213" s="2">
         <v>45199</v>
@@ -3819,11 +2978,10 @@
       <c r="C213" s="1">
         <v>0.75</v>
       </c>
-      <c r="D213" s="1"/>
-    </row>
-    <row r="214" spans="1:4">
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B214" s="2">
         <v>45291</v>
@@ -3831,11 +2989,10 @@
       <c r="C214" s="1">
         <v>0.83</v>
       </c>
-      <c r="D214" s="1"/>
-    </row>
-    <row r="215" spans="1:4">
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B215" s="2">
         <v>45382</v>
@@ -3843,11 +3000,10 @@
       <c r="C215" s="1">
         <v>0.8</v>
       </c>
-      <c r="D215" s="1"/>
-    </row>
-    <row r="216" spans="1:4">
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B216" s="2">
         <v>45473</v>
@@ -3855,11 +3011,10 @@
       <c r="C216" s="1">
         <v>0.8</v>
       </c>
-      <c r="D216" s="1"/>
-    </row>
-    <row r="217" spans="1:4">
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B217" s="2">
         <v>45565</v>
@@ -3867,11 +3022,10 @@
       <c r="C217" s="1">
         <v>0.8</v>
       </c>
-      <c r="D217" s="1"/>
-    </row>
-    <row r="218" spans="1:4">
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B218" s="2">
         <v>45657</v>
@@ -3879,11 +3033,10 @@
       <c r="C218" s="1">
         <v>0.8</v>
       </c>
-      <c r="D218" s="1"/>
-    </row>
-    <row r="219" spans="1:4">
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B219" s="2">
         <v>45747</v>
@@ -3891,11 +3044,10 @@
       <c r="C219" s="1">
         <v>0.8</v>
       </c>
-      <c r="D219" s="1"/>
-    </row>
-    <row r="220" spans="1:4">
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B220" s="2">
         <v>45838</v>
@@ -3903,11 +3055,10 @@
       <c r="C220" s="1">
         <v>0.8</v>
       </c>
-      <c r="D220" s="1"/>
-    </row>
-    <row r="221" spans="1:4">
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B221" s="2">
         <v>45930</v>
@@ -3915,11 +3066,10 @@
       <c r="C221" s="1">
         <v>0.8</v>
       </c>
-      <c r="D221" s="1"/>
-    </row>
-    <row r="222" spans="1:4">
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B222" s="2">
         <v>46022</v>
@@ -3927,11 +3077,10 @@
       <c r="C222" s="1">
         <v>0.9</v>
       </c>
-      <c r="D222" s="1"/>
-    </row>
-    <row r="223" spans="1:4">
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B223" s="2">
         <v>46112</v>
@@ -3939,11 +3088,10 @@
       <c r="C223" s="1">
         <v>0.8</v>
       </c>
-      <c r="D223" s="1"/>
-    </row>
-    <row r="224" spans="1:4">
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B224" s="2">
         <v>46203</v>
@@ -3951,11 +3099,10 @@
       <c r="C224" s="1">
         <v>0.8</v>
       </c>
-      <c r="D224" s="1"/>
-    </row>
-    <row r="225" spans="1:4">
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B225" s="2">
         <v>46295</v>
@@ -3963,11 +3110,10 @@
       <c r="C225" s="1">
         <v>0.8</v>
       </c>
-      <c r="D225" s="1"/>
-    </row>
-    <row r="226" spans="1:4">
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B226" s="2">
         <v>46387</v>
@@ -3975,11 +3121,10 @@
       <c r="C226" s="1">
         <v>0.9</v>
       </c>
-      <c r="D226" s="1"/>
-    </row>
-    <row r="227" spans="1:4">
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B227" s="2">
         <v>46477</v>
@@ -3987,11 +3132,10 @@
       <c r="C227" s="1">
         <v>0.8</v>
       </c>
-      <c r="D227" s="1"/>
-    </row>
-    <row r="228" spans="1:4">
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B228" s="2">
         <v>46568</v>
@@ -3999,11 +3143,10 @@
       <c r="C228" s="1">
         <v>0.8</v>
       </c>
-      <c r="D228" s="1"/>
-    </row>
-    <row r="229" spans="1:4">
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B229" s="2">
         <v>46660</v>
@@ -4011,11 +3154,10 @@
       <c r="C229" s="1">
         <v>0.8</v>
       </c>
-      <c r="D229" s="1"/>
-    </row>
-    <row r="230" spans="1:4">
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B230" s="2">
         <v>46752</v>
@@ -4023,11 +3165,10 @@
       <c r="C230" s="1">
         <v>0.9</v>
       </c>
-      <c r="D230" s="1"/>
-    </row>
-    <row r="231" spans="1:4">
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B231" s="2">
         <v>45016</v>
@@ -4035,23 +3176,21 @@
       <c r="C231" s="1">
         <v>15.73</v>
       </c>
-      <c r="D231" s="1"/>
-    </row>
-    <row r="232" spans="1:4">
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B232" s="2">
         <v>45107</v>
       </c>
       <c r="C232" s="1">
-        <v>16.06</v>
-      </c>
-      <c r="D232" s="1"/>
-    </row>
-    <row r="233" spans="1:4">
+        <v>16.059999999999999</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B233" s="2">
         <v>45199</v>
@@ -4059,11 +3198,10 @@
       <c r="C233" s="1">
         <v>16.27</v>
       </c>
-      <c r="D233" s="1"/>
-    </row>
-    <row r="234" spans="1:4">
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B234" s="2">
         <v>45291</v>
@@ -4071,11 +3209,10 @@
       <c r="C234" s="1">
         <v>16.37</v>
       </c>
-      <c r="D234" s="1"/>
-    </row>
-    <row r="235" spans="1:4">
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B235" s="2">
         <v>45382</v>
@@ -4083,23 +3220,21 @@
       <c r="C235" s="1">
         <v>16.7</v>
       </c>
-      <c r="D235" s="1"/>
-    </row>
-    <row r="236" spans="1:4">
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B236" s="2">
         <v>45473</v>
       </c>
       <c r="C236" s="1">
-        <v>16.6</v>
-      </c>
-      <c r="D236" s="1"/>
-    </row>
-    <row r="237" spans="1:4">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B237" s="2">
         <v>45565</v>
@@ -4107,35 +3242,32 @@
       <c r="C237" s="1">
         <v>16.8</v>
       </c>
-      <c r="D237" s="1"/>
-    </row>
-    <row r="238" spans="1:4">
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B238" s="2">
         <v>45657</v>
       </c>
       <c r="C238" s="1">
-        <v>17.1</v>
-      </c>
-      <c r="D238" s="1"/>
-    </row>
-    <row r="239" spans="1:4">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B239" s="2">
         <v>45747</v>
       </c>
       <c r="C239" s="1">
-        <v>16.9</v>
-      </c>
-      <c r="D239" s="1"/>
-    </row>
-    <row r="240" spans="1:4">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B240" s="2">
         <v>45838</v>
@@ -4143,35 +3275,32 @@
       <c r="C240" s="1">
         <v>16.5</v>
       </c>
-      <c r="D240" s="1"/>
-    </row>
-    <row r="241" spans="1:4">
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B241" s="2">
         <v>45930</v>
       </c>
       <c r="C241" s="1">
-        <v>17.1</v>
-      </c>
-      <c r="D241" s="1"/>
-    </row>
-    <row r="242" spans="1:4">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B242" s="2">
         <v>46022</v>
       </c>
       <c r="C242" s="1">
-        <v>17.1</v>
-      </c>
-      <c r="D242" s="1"/>
-    </row>
-    <row r="243" spans="1:4">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B243" s="2">
         <v>46112</v>
@@ -4179,11 +3308,10 @@
       <c r="C243" s="1">
         <v>17</v>
       </c>
-      <c r="D243" s="1"/>
-    </row>
-    <row r="244" spans="1:4">
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B244" s="2">
         <v>46203</v>
@@ -4191,11 +3319,10 @@
       <c r="C244" s="1">
         <v>16.7</v>
       </c>
-      <c r="D244" s="1"/>
-    </row>
-    <row r="245" spans="1:4">
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B245" s="2">
         <v>46295</v>
@@ -4203,11 +3330,10 @@
       <c r="C245" s="1">
         <v>17.3</v>
       </c>
-      <c r="D245" s="1"/>
-    </row>
-    <row r="246" spans="1:4">
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B246" s="2">
         <v>46387</v>
@@ -4215,11 +3341,10 @@
       <c r="C246" s="1">
         <v>17.3</v>
       </c>
-      <c r="D246" s="1"/>
-    </row>
-    <row r="247" spans="1:4">
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B247" s="2">
         <v>46477</v>
@@ -4227,23 +3352,21 @@
       <c r="C247" s="1">
         <v>17.2</v>
       </c>
-      <c r="D247" s="1"/>
-    </row>
-    <row r="248" spans="1:4">
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B248" s="2">
         <v>46568</v>
       </c>
       <c r="C248" s="1">
-        <v>16.9</v>
-      </c>
-      <c r="D248" s="1"/>
-    </row>
-    <row r="249" spans="1:4">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B249" s="2">
         <v>46660</v>
@@ -4251,11 +3374,10 @@
       <c r="C249" s="1">
         <v>17.5</v>
       </c>
-      <c r="D249" s="1"/>
-    </row>
-    <row r="250" spans="1:4">
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B250" s="2">
         <v>46752</v>
@@ -4263,10 +3385,9 @@
       <c r="C250" s="1">
         <v>17.5</v>
       </c>
-      <c r="D250" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>